--- a/Excel/columns.xlsx
+++ b/Excel/columns.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26202"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="133" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57C45E67-456E-4D02-B6BE-286A9327F587}"/>
+  <xr:revisionPtr revIDLastSave="135" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ADCA3DBD-1A96-4688-BAB2-C68E53EC87CC}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="41">
   <si>
     <t>dailies</t>
   </si>
@@ -558,7 +558,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
@@ -797,7 +797,7 @@
         <v>31</v>
       </c>
       <c r="E20">
-        <f t="shared" ref="E20:E31" si="1">E19+1</f>
+        <f t="shared" ref="E20:E27" si="1">E19+1</f>
         <v>2</v>
       </c>
     </row>
@@ -887,7 +887,7 @@
         <v>8</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="D26" s="10" t="s">
         <v>37</v>
@@ -903,7 +903,7 @@
         <v>9</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>39</v>
@@ -919,7 +919,7 @@
         <v>10</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>40</v>
@@ -934,7 +934,7 @@
         <v>11</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="D29" s="1"/>
     </row>
@@ -944,7 +944,7 @@
         <v>12</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="D30" s="1"/>
     </row>
@@ -953,18 +953,10 @@
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B31" s="1" t="s">
-        <v>17</v>
+      <c r="B31" t="s">
+        <v>6</v>
       </c>
       <c r="D31" s="1"/>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32">
-        <v>14</v>
-      </c>
-      <c r="B32" t="s">
-        <v>6</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
